--- a/packages/examples/showcase/executive-board-pack/artifact/executive-board-pack.xlsx
+++ b/packages/examples/showcase/executive-board-pack/artifact/executive-board-pack.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Board Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Regional Views" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -687,6 +688,20 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2"/>
@@ -1092,6 +1107,14 @@
       <c r="A15" s="16" t="s">
         <v>44</v>
       </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="17"/>
@@ -1338,12 +1361,24 @@
       <c r="A1" s="30" t="s">
         <v>20</v>
       </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
       <c r="H1" s="42" t="s">
         <v>25</v>
       </c>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
       <c r="O1" s="54" t="s">
         <v>30</v>
       </c>
+      <c r="P1" s="54"/>
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="31"/>
